--- a/2026_09_21/LSLS/report_for_BD_template.xlsx
+++ b/2026_09_21/LSLS/report_for_BD_template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_21\LSLS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61DB595-1C44-4943-ADF9-52245B43D2B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="45" windowWidth="13395" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19560" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reduction of salt.sugar" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="14">
   <si>
     <t>Web</t>
   </si>
@@ -68,11 +74,26 @@
   <si>
     <t>user_share_poi</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">少鹽少糖食店 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Daily Theme Listing Impressions (adv search)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -213,6 +234,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -260,7 +284,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -293,9 +317,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -328,6 +369,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -503,8 +561,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -782,6 +840,25 @@
       <c r="D38" s="13"/>
       <c r="E38" s="15"/>
     </row>
+    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -789,7 +866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1043,7 +1120,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/2026_09_21/LSLS/report_for_BD_template.xlsx
+++ b/2026_09_21/LSLS/report_for_BD_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_21\LSLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61DB595-1C44-4943-ADF9-52245B43D2B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DECF2C-48B5-4327-9E2D-5C4F18E7C005}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19560" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="15">
   <si>
     <t>Web</t>
   </si>
@@ -54,9 +54,6 @@
     </r>
   </si>
   <si>
-    <t>少鹽少糖食店 icon impression</t>
-  </si>
-  <si>
     <t>Mobile Web</t>
   </si>
   <si>
@@ -86,7 +83,25 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Daily Theme Listing Impressions (adv search)</t>
+      <t>Daily Theme Listing Impressions</t>
+    </r>
+  </si>
+  <si>
+    <t>少鹽少糖食店 Daily Badge impression by device</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">少鹽少糖食店 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Daily Brand Page (LMS) Pageview/ Impressions</t>
     </r>
   </si>
 </sst>
@@ -562,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -601,7 +616,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
@@ -614,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>1</v>
@@ -842,22 +857,345 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5" t="s">
+      <c r="A42" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
+      <c r="A43" s="11"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="11"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="11"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="11"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="13"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="13"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="11"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="11"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="11"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="11"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="11"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="11"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="11"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="11"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="11"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="11"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="11"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="11"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="11"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="11"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="11"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="11"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="11"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="11"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="11"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="11"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="11"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+    </row>
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="13"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="13"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="11"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="11"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="13"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="11"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="13"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="13"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="13"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="11"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="11"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="11"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="13"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="11"/>
+      <c r="B91" s="13"/>
+      <c r="C91" s="13"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="11"/>
+      <c r="B92" s="13"/>
+      <c r="C92" s="13"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="11"/>
+      <c r="B93" s="13"/>
+      <c r="C93" s="13"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="11"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="11"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="11"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="11"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="11"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="11"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="11"/>
+      <c r="B100" s="13"/>
+      <c r="C100" s="13"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="11"/>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="11"/>
+      <c r="B102" s="13"/>
+      <c r="C102" s="13"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="11"/>
+      <c r="B103" s="13"/>
+      <c r="C103" s="13"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="11"/>
+      <c r="B104" s="13"/>
+      <c r="C104" s="13"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="11"/>
+      <c r="B105" s="13"/>
+      <c r="C105" s="13"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="11"/>
+      <c r="B106" s="13"/>
+      <c r="C106" s="13"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="11"/>
+      <c r="B107" s="13"/>
+      <c r="C107" s="13"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="11"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -875,7 +1213,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -888,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>1</v>
@@ -1131,199 +1469,199 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/2026_09_21/LSLS/report_for_BD_template.xlsx
+++ b/2026_09_21/LSLS/report_for_BD_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_21\LSLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DECF2C-48B5-4327-9E2D-5C4F18E7C005}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A737500-7964-428E-B785-FBF4DB3E7721}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19560" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,21 +37,6 @@
   </si>
   <si>
     <t>App</t>
-  </si>
-  <si>
-    <r>
-      <t>少鹽少糖食店</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SR1 page view</t>
-    </r>
   </si>
   <si>
     <t>Mobile Web</t>
@@ -83,11 +68,23 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Daily Theme Listing Impressions</t>
+      <t>Daily Brand Page (LMS) Pageview/ Impressions</t>
     </r>
   </si>
   <si>
-    <t>少鹽少糖食店 Daily Badge impression by device</t>
+    <r>
+      <t>少鹽少糖食店</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Daily Theme Listing Impressions</t>
+    </r>
   </si>
   <si>
     <r>
@@ -101,7 +98,23 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Daily Brand Page (LMS) Pageview/ Impressions</t>
+      <t>SR1 page view</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">少鹽少糖食店 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Daily Badge impression by device</t>
     </r>
   </si>
 </sst>
@@ -109,7 +122,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +173,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -587,7 +608,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -616,7 +637,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
@@ -629,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>1</v>
@@ -857,7 +878,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1213,7 +1234,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1226,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>1</v>
@@ -1469,199 +1490,199 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/2026_09_21/LSLS/report_for_BD_template.xlsx
+++ b/2026_09_21/LSLS/report_for_BD_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_21\LSLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A737500-7964-428E-B785-FBF4DB3E7721}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A8EC71-5866-460B-8C5E-304DF6A73F54}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19560" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
